--- a/results/components/gene_names/p8s4.xlsx
+++ b/results/components/gene_names/p8s4.xlsx
@@ -22,28 +22,28 @@
     <t>gene2</t>
   </si>
   <si>
-    <t>Psn</t>
-  </si>
-  <si>
-    <t>Ark</t>
-  </si>
-  <si>
-    <t>cnc</t>
-  </si>
-  <si>
-    <t>Tak1</t>
-  </si>
-  <si>
-    <t>ttk</t>
-  </si>
-  <si>
-    <t>ALiX</t>
-  </si>
-  <si>
-    <t>CG9445</t>
-  </si>
-  <si>
-    <t>puc</t>
+    <t>Ef1gamma</t>
+  </si>
+  <si>
+    <t>tin</t>
+  </si>
+  <si>
+    <t>sas</t>
+  </si>
+  <si>
+    <t>spen</t>
+  </si>
+  <si>
+    <t>Eip63E</t>
+  </si>
+  <si>
+    <t>abd-A</t>
+  </si>
+  <si>
+    <t>rad50</t>
+  </si>
+  <si>
+    <t>sec23</t>
   </si>
 </sst>
 </file>

--- a/results/components/gene_names/p8s4.xlsx
+++ b/results/components/gene_names/p8s4.xlsx
@@ -22,28 +22,28 @@
     <t>gene2</t>
   </si>
   <si>
-    <t>Ef1gamma</t>
-  </si>
-  <si>
-    <t>tin</t>
-  </si>
-  <si>
-    <t>sas</t>
-  </si>
-  <si>
-    <t>spen</t>
-  </si>
-  <si>
-    <t>Eip63E</t>
-  </si>
-  <si>
-    <t>abd-A</t>
-  </si>
-  <si>
-    <t>rad50</t>
-  </si>
-  <si>
-    <t>sec23</t>
+    <t>Syx1A</t>
+  </si>
+  <si>
+    <t>CG32082</t>
+  </si>
+  <si>
+    <t>Crk</t>
+  </si>
+  <si>
+    <t>RpL30</t>
+  </si>
+  <si>
+    <t>Nrt</t>
+  </si>
+  <si>
+    <t>Akt1</t>
+  </si>
+  <si>
+    <t>Myo31DF</t>
+  </si>
+  <si>
+    <t>amx</t>
   </si>
 </sst>
 </file>
